--- a/artfynd/A 5713-2026 artfynd.xlsx
+++ b/artfynd/A 5713-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110915913</v>
+        <v>101689326</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedemora (Hedemora), Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564144.4249848794</v>
+        <v>564140</v>
       </c>
       <c r="R2" t="n">
-        <v>6703124.943041676</v>
+        <v>6703132</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,55 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110920184</v>
+        <v>110915913</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedemora (Hedemora), Dlr</t>
+          <t>Hedemora, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564135.5119094957</v>
+        <v>564144</v>
       </c>
       <c r="R3" t="n">
-        <v>6703209.647781903</v>
+        <v>6703125</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,12 +894,7 @@
         <v>110920187</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,14 +923,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedemora (Hedemora), Dlr</t>
+          <t>Hedemora, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564137.6306254512</v>
+        <v>564137</v>
       </c>
       <c r="R4" t="n">
-        <v>6703117.915204225</v>
+        <v>6703117</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,54 +999,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110915985</v>
+        <v>111274261</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedemora (Hedemora), Dlr</t>
+          <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564149.2050964383</v>
+        <v>564141</v>
       </c>
       <c r="R5" t="n">
-        <v>6703217.784399151</v>
+        <v>6703116</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>21:28</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>21:28</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,53 +1096,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111274273</v>
+        <v>121905268</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564172.1486391345</v>
+        <v>564170</v>
       </c>
       <c r="R6" t="n">
-        <v>6703150.103735355</v>
+        <v>6703165</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111274261</v>
+        <v>110915985</v>
       </c>
       <c r="B7" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,37 +1209,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallbäck, Dlr</t>
+          <t>Hedemora, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564141.617945264</v>
+        <v>564149</v>
       </c>
       <c r="R7" t="n">
-        <v>6703116.01224305</v>
+        <v>6703218</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1264,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111274269</v>
+        <v>110920184</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,19 +1335,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallbäck, Dlr</t>
+          <t>Hedemora, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564170.172467586</v>
+        <v>564136</v>
       </c>
       <c r="R8" t="n">
-        <v>6703150.068720036</v>
+        <v>6703210</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,27 +1376,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Blomning</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1400,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,12 +1421,7 @@
         <v>111274267</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564177.8062000184</v>
+        <v>564178</v>
       </c>
       <c r="R9" t="n">
-        <v>6703165.499034845</v>
+        <v>6703165</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1546,19 +1486,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1591,15 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111274272</v>
+        <v>111274268</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564178.9953147708</v>
+        <v>564190</v>
       </c>
       <c r="R10" t="n">
-        <v>6703154.172173821</v>
+        <v>6703141</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1664,19 +1589,14 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Blomning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,6 +1605,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,15 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111274271</v>
+        <v>111274269</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564189.033516159</v>
+        <v>564170</v>
       </c>
       <c r="R11" t="n">
-        <v>6703145.469057793</v>
+        <v>6703150</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1776,19 +1692,14 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blomning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,6 +1708,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1815,15 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111274268</v>
+        <v>111274270</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564190.0915398612</v>
+        <v>564182</v>
       </c>
       <c r="R12" t="n">
-        <v>6703141.540684599</v>
+        <v>6703122</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1888,33 +1795,17 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Blomning</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1933,15 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111274270</v>
+        <v>111274271</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1973,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564182.5277345474</v>
+        <v>564189</v>
       </c>
       <c r="R13" t="n">
-        <v>6703122.164335305</v>
+        <v>6703145</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2006,19 +1892,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,58 +1921,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121905268</v>
+        <v>111274272</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallbäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564170</v>
+        <v>564179</v>
       </c>
       <c r="R14" t="n">
-        <v>6703165</v>
+        <v>6703154</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,12 +1986,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,6 +2015,103 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111274273</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kallbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564172</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6703150</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5713-2026 artfynd.xlsx
+++ b/artfynd/A 5713-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101689326</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110915913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110920187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274261</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121905268</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110915985</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110920184</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274267</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274268</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274269</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274270</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2112,8 +2182,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111274273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>